--- a/evidence/pg16_normal_sample_2.xlsx
+++ b/evidence/pg16_normal_sample_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>9fe67789c6f129d0aba53d6089e81870</t>
+    <t>28f87bc107aa00e77eef90beeb9d35f9</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>1f1c3d9c6bc40c968258787dd247ed2a</t>
+    <t>94c6b6b1d932374d6e1635a01129389f</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T06:11:57Z</t>
+    <t>2026-10-26T06:23:42Z</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/pg16_normal_sample_2.xlsx
+++ b/evidence/pg16_normal_sample_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>279ba9d28e897277d9f8f4ff3e400c2b</t>
+    <t>6268f1867daedc75cb9579afafcefa29</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>dbe98f217b6b1b0410e6afd9588cefec</t>
+    <t>a28305590214e8429a639af050482f94</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T07:04:55Z</t>
+    <t>2026-10-26T07:29:02Z</t>
   </si>
   <si>
     <t>precision</t>
